--- a/downloads/srilanka_franchise_stores.xlsx
+++ b/downloads/srilanka_franchise_stores.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$77</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="302">
   <si>
     <t>Address line 1</t>
   </si>
@@ -107,9 +107,6 @@
     <t>ENDERAMULLA</t>
   </si>
   <si>
-    <t>FACTORY</t>
-  </si>
-  <si>
     <t>GAMPAHA</t>
   </si>
   <si>
@@ -266,9 +263,6 @@
     <t>YAKKALA</t>
   </si>
   <si>
-    <t>NA</t>
-  </si>
-  <si>
     <t>Sales</t>
   </si>
   <si>
@@ -933,9 +927,6 @@
   </si>
   <si>
     <t>Pepiliyana</t>
-  </si>
-  <si>
-    <t>011 293 7008</t>
   </si>
   <si>
     <t>From Date</t>
@@ -1279,7 +1270,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M78"/>
+  <dimension ref="A1:M77"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="19.1796875" customWidth="1"/>
@@ -1316,19 +1307,19 @@
         <v>5</v>
       </c>
       <c r="I1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K1" t="s">
         <v>80</v>
       </c>
-      <c r="J1" t="s">
-        <v>81</v>
-      </c>
-      <c r="K1" t="s">
-        <v>82</v>
-      </c>
       <c r="L1" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="M1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
@@ -1336,19 +1327,19 @@
         <v>2120</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E2">
         <v>10280</v>
       </c>
       <c r="F2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G2">
         <v>6.8455221000000002</v>
@@ -1363,7 +1354,7 @@
         <v>259876</v>
       </c>
       <c r="K2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L2" s="3">
         <v>45901</v>
@@ -1377,19 +1368,19 @@
         <v>2121</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E3">
         <v>11000</v>
       </c>
       <c r="F3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G3">
         <v>7.0937279000000002</v>
@@ -1404,7 +1395,7 @@
         <v>410872</v>
       </c>
       <c r="K3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L3" s="3">
         <v>45901</v>
@@ -1419,19 +1410,19 @@
         <v>2103</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E4">
         <v>11850</v>
       </c>
       <c r="F4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G4">
         <v>7.0029526000000004</v>
@@ -1446,7 +1437,7 @@
         <v>315939</v>
       </c>
       <c r="K4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L4" s="3">
         <v>45901</v>
@@ -1464,16 +1455,16 @@
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E5">
         <v>400</v>
       </c>
       <c r="F5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G5">
         <v>6.8875991000000001</v>
@@ -1488,7 +1479,7 @@
         <v>496201</v>
       </c>
       <c r="K5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L5" s="3">
         <v>45901</v>
@@ -1506,16 +1497,16 @@
         <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E6">
         <v>800</v>
       </c>
       <c r="F6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G6">
         <v>6.9164840999999999</v>
@@ -1530,7 +1521,7 @@
         <v>554359</v>
       </c>
       <c r="K6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L6" s="3">
         <v>45901</v>
@@ -1545,19 +1536,19 @@
         <v>2119</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E7">
         <v>10400</v>
       </c>
       <c r="F7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G7">
         <v>6.7792691999999999</v>
@@ -1572,7 +1563,7 @@
         <v>657346</v>
       </c>
       <c r="K7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L7" s="3">
         <v>45901</v>
@@ -1587,19 +1578,19 @@
         <v>2106</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E8">
         <v>12500</v>
       </c>
       <c r="F8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G8">
         <v>6.7111343999999997</v>
@@ -1614,7 +1605,7 @@
         <v>187053</v>
       </c>
       <c r="K8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L8" s="3">
         <v>45901</v>
@@ -1632,16 +1623,16 @@
         <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E9">
         <v>100</v>
       </c>
       <c r="F9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G9">
         <v>6.9344910999999998</v>
@@ -1656,7 +1647,7 @@
         <v>173062</v>
       </c>
       <c r="K9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L9" s="3">
         <v>45901</v>
@@ -1671,19 +1662,19 @@
         <v>2124</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D10" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E10">
         <v>11300</v>
       </c>
       <c r="F10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G10">
         <v>6.9817419000000003</v>
@@ -1698,7 +1689,7 @@
         <v>492825</v>
       </c>
       <c r="K10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L10" s="3">
         <v>45901</v>
@@ -1713,19 +1704,19 @@
         <v>2126</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D11" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E11">
         <v>10115</v>
       </c>
       <c r="F11" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G11">
         <v>6.9078727000000004</v>
@@ -1740,7 +1731,7 @@
         <v>394168</v>
       </c>
       <c r="K11" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L11" s="3">
         <v>45901</v>
@@ -1758,16 +1749,16 @@
         <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E12">
         <v>1500</v>
       </c>
       <c r="F12" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G12">
         <v>6.9217535999999997</v>
@@ -1782,7 +1773,7 @@
         <v>522061</v>
       </c>
       <c r="K12" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L12" s="3">
         <v>45901</v>
@@ -1797,19 +1788,19 @@
         <v>2063</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C13" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D13" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E13">
         <v>500</v>
       </c>
       <c r="F13" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G13">
         <v>6.8927728999999998</v>
@@ -1824,7 +1815,7 @@
         <v>170508</v>
       </c>
       <c r="K13" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L13" s="3">
         <v>45901</v>
@@ -1839,19 +1830,19 @@
         <v>2135</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D14" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E14">
         <v>10230</v>
       </c>
       <c r="F14" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G14">
         <v>6.8356757000000004</v>
@@ -1866,7 +1857,7 @@
         <v>279032</v>
       </c>
       <c r="K14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L14" s="3">
         <v>45901</v>
@@ -1881,19 +1872,19 @@
         <v>2132</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D15" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E15">
         <v>11640</v>
       </c>
       <c r="F15" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G15">
         <v>6.9741152</v>
@@ -1908,7 +1899,7 @@
         <v>357196</v>
       </c>
       <c r="K15" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L15" s="3">
         <v>45901</v>
@@ -1923,19 +1914,19 @@
         <v>2068</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C16" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D16" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E16">
         <v>11500</v>
       </c>
       <c r="F16" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G16">
         <v>7.2003575</v>
@@ -1950,7 +1941,7 @@
         <v>299165</v>
       </c>
       <c r="K16" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L16" s="3">
         <v>45901</v>
@@ -1965,19 +1956,19 @@
         <v>2139</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C17" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D17" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E17">
         <v>10116</v>
       </c>
       <c r="F17" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G17">
         <v>6.9153082000000001</v>
@@ -1992,7 +1983,7 @@
         <v>405467</v>
       </c>
       <c r="K17" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L17" s="3">
         <v>45901</v>
@@ -2007,19 +1998,19 @@
         <v>2094</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C18" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D18" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E18">
         <v>1000</v>
       </c>
       <c r="F18" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G18">
         <v>6.9351640999999997</v>
@@ -2034,7 +2025,7 @@
         <v>341399</v>
       </c>
       <c r="K18" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L18" s="3">
         <v>45901</v>
@@ -2049,19 +2040,19 @@
         <v>2111</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C19" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D19" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E19">
         <v>11010</v>
       </c>
       <c r="F19" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G19">
         <v>7.0302160999999996</v>
@@ -2076,7 +2067,7 @@
         <v>371659</v>
       </c>
       <c r="K19" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L19" s="3">
         <v>45901</v>
@@ -2091,19 +2082,19 @@
         <v>2115</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C20" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D20" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E20">
         <v>11350</v>
       </c>
       <c r="F20" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G20">
         <v>7.0815678999999996</v>
@@ -2118,7 +2109,7 @@
         <v>332848</v>
       </c>
       <c r="K20" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L20" s="3">
         <v>45901</v>
@@ -2133,19 +2124,19 @@
         <v>2082</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C21" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D21" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E21">
         <v>200</v>
       </c>
       <c r="F21" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G21">
         <v>6.9258350999999996</v>
@@ -2160,7 +2151,7 @@
         <v>409978</v>
       </c>
       <c r="K21" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L21" s="3">
         <v>45901</v>
@@ -2175,19 +2166,19 @@
         <v>2061</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C22" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D22" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E22">
         <v>11450</v>
       </c>
       <c r="F22" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G22">
         <v>7.1718095000000002</v>
@@ -2202,7 +2193,7 @@
         <v>336451</v>
       </c>
       <c r="K22" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L22" s="3">
         <v>45901</v>
@@ -2217,19 +2208,19 @@
         <v>2085</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C23" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D23" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E23">
         <v>1400</v>
       </c>
       <c r="F23" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G23">
         <v>6.9460465999999998</v>
@@ -2244,7 +2235,7 @@
         <v>559998</v>
       </c>
       <c r="K23" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L23" s="3">
         <v>45901</v>
@@ -2259,19 +2250,19 @@
         <v>2073</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D24" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E24">
         <v>10600</v>
       </c>
       <c r="F24" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G24">
         <v>6.9325045999999997</v>
@@ -2286,7 +2277,7 @@
         <v>287324</v>
       </c>
       <c r="K24" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L24" s="3">
         <v>45901</v>
@@ -2301,19 +2292,19 @@
         <v>2130</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C25" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D25" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E25">
         <v>10100</v>
       </c>
       <c r="F25" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G25">
         <v>6.8778813000000003</v>
@@ -2328,7 +2319,7 @@
         <v>316034</v>
       </c>
       <c r="K25" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L25" s="3">
         <v>45901</v>
@@ -2343,19 +2334,19 @@
         <v>2125</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C26" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D26" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E26">
         <v>11300</v>
       </c>
       <c r="F26" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G26">
         <v>6.9528648999999998</v>
@@ -2370,7 +2361,7 @@
         <v>244549</v>
       </c>
       <c r="K26" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L26" s="3">
         <v>45901</v>
@@ -2385,19 +2376,19 @@
         <v>2131</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C27" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D27" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E27">
         <v>10350</v>
       </c>
       <c r="F27" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G27">
         <v>6.8660585000000003</v>
@@ -2412,7 +2403,7 @@
         <v>296049</v>
       </c>
       <c r="K27" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L27" s="3">
         <v>45901</v>
@@ -2430,16 +2421,16 @@
         <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D28" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E28">
         <v>10290</v>
       </c>
       <c r="F28" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G28">
         <v>6.8263601999999999</v>
@@ -2454,7 +2445,7 @@
         <v>364562</v>
       </c>
       <c r="K28" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L28" s="3">
         <v>45901</v>
@@ -2469,19 +2460,19 @@
         <v>2098</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C29" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D29" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E29">
         <v>71722</v>
       </c>
       <c r="F29" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G29">
         <v>7.0212743</v>
@@ -2496,7 +2487,7 @@
         <v>368364</v>
       </c>
       <c r="K29" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L29" s="3">
         <v>45901</v>
@@ -2511,19 +2502,19 @@
         <v>2141</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C30" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D30" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E30">
         <v>11880</v>
       </c>
       <c r="F30" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G30">
         <v>7.1411595999999999</v>
@@ -2538,7 +2529,7 @@
         <v>213978</v>
       </c>
       <c r="K30" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L30" s="3">
         <v>45901</v>
@@ -2553,19 +2544,19 @@
         <v>2114</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C31" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D31" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E31">
         <v>10600</v>
       </c>
       <c r="F31" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G31">
         <v>6.9368650000000001</v>
@@ -2580,7 +2571,7 @@
         <v>344866</v>
       </c>
       <c r="K31" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L31" s="3">
         <v>45901</v>
@@ -2595,19 +2586,19 @@
         <v>2123</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C32" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D32" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E32">
         <v>10600</v>
       </c>
       <c r="F32" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G32">
         <v>6.9358282000000004</v>
@@ -2622,7 +2613,7 @@
         <v>322107</v>
       </c>
       <c r="K32" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L32" s="3">
         <v>45901</v>
@@ -2640,16 +2631,16 @@
         <v>11</v>
       </c>
       <c r="C33" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D33" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E33">
         <v>700</v>
       </c>
       <c r="F33" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G33">
         <v>6.9129674999999997</v>
@@ -2664,7 +2655,7 @@
         <v>419051</v>
       </c>
       <c r="K33" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L33" s="3">
         <v>45901</v>
@@ -2679,19 +2670,19 @@
         <v>2067</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C34" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D34" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E34">
         <v>500</v>
       </c>
       <c r="F34" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G34">
         <v>6.8882485999999998</v>
@@ -2706,7 +2697,7 @@
         <v>291130</v>
       </c>
       <c r="K34" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L34" s="3">
         <v>45901</v>
@@ -2724,16 +2715,16 @@
         <v>24</v>
       </c>
       <c r="C35" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D35" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E35">
         <v>10280</v>
       </c>
       <c r="F35" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G35">
         <v>6.8459449000000001</v>
@@ -2748,7 +2739,7 @@
         <v>265522</v>
       </c>
       <c r="K35" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L35" s="3">
         <v>45901</v>
@@ -2763,19 +2754,19 @@
         <v>2100</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C36" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D36" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E36">
         <v>600</v>
       </c>
       <c r="F36" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G36">
         <v>6.8714465999999996</v>
@@ -2790,7 +2781,7 @@
         <v>266427</v>
       </c>
       <c r="K36" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L36" s="3">
         <v>45901</v>
@@ -2805,19 +2796,19 @@
         <v>2076</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C37" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D37" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E37">
         <v>1400</v>
       </c>
       <c r="F37" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G37">
         <v>6.9475312000000002</v>
@@ -2832,7 +2823,7 @@
         <v>289252</v>
       </c>
       <c r="K37" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L37" s="3">
         <v>45901</v>
@@ -2847,19 +2838,19 @@
         <v>2088</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C38" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D38" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E38">
         <v>11500</v>
       </c>
       <c r="F38" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G38">
         <v>7.2249093999999996</v>
@@ -2874,7 +2865,7 @@
         <v>297938</v>
       </c>
       <c r="K38" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L38" s="3">
         <v>45901</v>
@@ -2889,19 +2880,19 @@
         <v>2109</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C39" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D39" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E39">
         <v>10600</v>
       </c>
       <c r="F39" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G39">
         <v>6.9240722000000003</v>
@@ -2916,7 +2907,7 @@
         <v>399068</v>
       </c>
       <c r="K39" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L39" s="3">
         <v>45901</v>
@@ -2931,19 +2922,19 @@
         <v>2112</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C40" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D40" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E40">
         <v>600</v>
       </c>
       <c r="F40" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G40">
         <v>6.8780495999999998</v>
@@ -2958,7 +2949,7 @@
         <v>312993</v>
       </c>
       <c r="K40" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L40" s="3">
         <v>45901</v>
@@ -2973,19 +2964,19 @@
         <v>2134</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C41" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D41" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E41">
         <v>10350</v>
       </c>
       <c r="F41" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G41">
         <v>6.8497769000000002</v>
@@ -3000,7 +2991,7 @@
         <v>260912</v>
       </c>
       <c r="K41" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L41" s="3">
         <v>45901</v>
@@ -3015,19 +3006,19 @@
         <v>2147</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C42" t="s">
+        <v>203</v>
+      </c>
+      <c r="D42" t="s">
         <v>204</v>
-      </c>
-      <c r="C42" t="s">
-        <v>205</v>
-      </c>
-      <c r="D42" t="s">
-        <v>206</v>
       </c>
       <c r="E42">
         <v>12000</v>
       </c>
       <c r="F42" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G42">
         <v>6.5778147999999996</v>
@@ -3042,7 +3033,7 @@
         <v>146130</v>
       </c>
       <c r="K42" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L42" s="3">
         <v>45901</v>
@@ -3057,19 +3048,19 @@
         <v>2064</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C43" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D43" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E43">
         <v>1000</v>
       </c>
       <c r="F43" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G43">
         <v>6.9232554999999998</v>
@@ -3084,7 +3075,7 @@
         <v>463415</v>
       </c>
       <c r="K43" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L43" s="3">
         <v>45901</v>
@@ -3102,16 +3093,16 @@
         <v>15</v>
       </c>
       <c r="C44" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D44" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E44">
         <v>10120</v>
       </c>
       <c r="F44" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G44">
         <v>6.9020231000000001</v>
@@ -3126,7 +3117,7 @@
         <v>267050</v>
       </c>
       <c r="K44" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L44" s="3">
         <v>45901</v>
@@ -3141,19 +3132,19 @@
         <v>2136</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C45" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D45" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E45">
         <v>1100</v>
       </c>
       <c r="F45" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G45">
         <v>6.9365573999999999</v>
@@ -3168,7 +3159,7 @@
         <v>298713</v>
       </c>
       <c r="K45" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L45" s="3">
         <v>45901</v>
@@ -3183,19 +3174,19 @@
         <v>2097</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C46" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D46" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E46">
         <v>10100</v>
       </c>
       <c r="F46" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G46">
         <v>6.9152107999999997</v>
@@ -3210,7 +3201,7 @@
         <v>351752</v>
       </c>
       <c r="K46" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L46" s="3">
         <v>45901</v>
@@ -3225,19 +3216,19 @@
         <v>2074</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C47" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D47" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E47">
         <v>11500</v>
       </c>
       <c r="F47" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G47">
         <v>7.2111095000000001</v>
@@ -3252,7 +3243,7 @@
         <v>494046</v>
       </c>
       <c r="K47" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L47" s="3">
         <v>45901</v>
@@ -3267,19 +3258,19 @@
         <v>2107</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C48" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D48" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E48">
         <v>10370</v>
       </c>
       <c r="F48" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G48">
         <v>6.8381759000000004</v>
@@ -3294,7 +3285,7 @@
         <v>554602</v>
       </c>
       <c r="K48" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L48" s="3">
         <v>45901</v>
@@ -3312,16 +3303,16 @@
         <v>16</v>
       </c>
       <c r="C49" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D49" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E49">
         <v>1500</v>
       </c>
       <c r="F49" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G49">
         <v>6.9614196000000002</v>
@@ -3336,7 +3327,7 @@
         <v>310177</v>
       </c>
       <c r="K49" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L49" s="3">
         <v>45901</v>
@@ -3354,7 +3345,7 @@
         <v>8</v>
       </c>
       <c r="C50" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D50" t="s">
         <v>8</v>
@@ -3363,7 +3354,7 @@
         <v>11320</v>
       </c>
       <c r="F50" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G50">
         <v>7.0479529999999997</v>
@@ -3378,7 +3369,7 @@
         <v>397643</v>
       </c>
       <c r="K50" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L50" s="3">
         <v>45901</v>
@@ -3393,19 +3384,19 @@
         <v>2138</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C51" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D51" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E51">
         <v>11870</v>
       </c>
       <c r="F51" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G51">
         <v>7.0854156000000001</v>
@@ -3420,7 +3411,7 @@
         <v>294003</v>
       </c>
       <c r="K51" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L51" s="3">
         <v>45901</v>
@@ -3435,19 +3426,19 @@
         <v>2069</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C52" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D52" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E52">
         <v>1500</v>
       </c>
       <c r="F52" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="G52">
         <v>6.9719439999999997</v>
@@ -3462,7 +3453,7 @@
         <v>411749</v>
       </c>
       <c r="K52" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L52" s="3">
         <v>45901</v>
@@ -3480,16 +3471,16 @@
         <v>19</v>
       </c>
       <c r="C53" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D53" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E53">
         <v>800</v>
       </c>
       <c r="F53" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G53">
         <v>6.9110851999999996</v>
@@ -3504,7 +3495,7 @@
         <v>418888</v>
       </c>
       <c r="K53" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L53" s="3">
         <v>45901</v>
@@ -3522,16 +3513,16 @@
         <v>21</v>
       </c>
       <c r="C54" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D54" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E54">
         <v>11300</v>
       </c>
       <c r="F54" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G54">
         <v>6.9710492999999998</v>
@@ -3546,7 +3537,7 @@
         <v>188231</v>
       </c>
       <c r="K54" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L54" s="3">
         <v>45901</v>
@@ -3564,7 +3555,7 @@
         <v>10</v>
       </c>
       <c r="C55" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D55" t="s">
         <v>10</v>
@@ -3573,7 +3564,7 @@
         <v>10250</v>
       </c>
       <c r="F55" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G55">
         <v>6.8744066000000004</v>
@@ -3588,7 +3579,7 @@
         <v>175268</v>
       </c>
       <c r="K55" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L55" s="3">
         <v>45901</v>
@@ -3606,16 +3597,16 @@
         <v>13</v>
       </c>
       <c r="C56" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D56" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E56">
         <v>10350</v>
       </c>
       <c r="F56" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="G56">
         <v>6.8352849000000004</v>
@@ -3630,7 +3621,7 @@
         <v>241339</v>
       </c>
       <c r="K56" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L56" s="3">
         <v>45901</v>
@@ -3645,19 +3636,19 @@
         <v>2075</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C57" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D57" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E57">
         <v>11400</v>
       </c>
       <c r="F57" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G57">
         <v>7.1389275999999997</v>
@@ -3672,7 +3663,7 @@
         <v>293474</v>
       </c>
       <c r="K57" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L57" s="3">
         <f>L56</f>
@@ -3691,7 +3682,7 @@
         <v>9</v>
       </c>
       <c r="C58" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D58" t="s">
         <v>9</v>
@@ -3700,7 +3691,7 @@
         <v>11100</v>
       </c>
       <c r="F58" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G58">
         <v>7.1266555</v>
@@ -3715,10 +3706,10 @@
         <v>278748</v>
       </c>
       <c r="K58" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L58" s="3">
-        <f t="shared" ref="L58:L78" si="1">L57</f>
+        <f t="shared" ref="L58:L77" si="1">L57</f>
         <v>45901</v>
       </c>
       <c r="M58" s="3">
@@ -3731,19 +3722,19 @@
         <v>2060</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C59" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D59" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E59">
         <v>11300</v>
       </c>
       <c r="F59" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G59">
         <v>6.9964677999999996</v>
@@ -3758,7 +3749,7 @@
         <v>330069</v>
       </c>
       <c r="K59" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L59" s="3">
         <f t="shared" si="1"/>
@@ -3774,19 +3765,19 @@
         <v>2102</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C60" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D60" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E60">
         <v>11600</v>
       </c>
       <c r="F60" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G60">
         <v>6.9806980000000003</v>
@@ -3801,7 +3792,7 @@
         <v>164605</v>
       </c>
       <c r="K60" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L60" s="3">
         <f t="shared" si="1"/>
@@ -3817,19 +3808,19 @@
         <v>2118</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C61" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D61" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E61">
         <v>600</v>
       </c>
       <c r="F61" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G61">
         <v>6.8769742000000003</v>
@@ -3844,7 +3835,7 @@
         <v>243370</v>
       </c>
       <c r="K61" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L61" s="3">
         <f t="shared" si="1"/>
@@ -3860,19 +3851,19 @@
         <v>2096</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C62" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D62" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E62">
         <v>1500</v>
       </c>
       <c r="F62" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="G62">
         <v>6.9568193999999997</v>
@@ -3887,7 +3878,7 @@
         <v>325187412</v>
       </c>
       <c r="K62" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L62" s="3">
         <f t="shared" si="1"/>
@@ -3906,16 +3897,16 @@
         <v>25</v>
       </c>
       <c r="C63" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D63" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E63">
         <v>11300</v>
       </c>
       <c r="F63" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G63">
         <v>6.9939945000000003</v>
@@ -3930,7 +3921,7 @@
         <v>331578</v>
       </c>
       <c r="K63" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L63" s="3">
         <f t="shared" si="1"/>
@@ -3946,19 +3937,19 @@
         <v>2117</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C64" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D64" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E64">
         <v>100</v>
       </c>
       <c r="F64" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G64">
         <v>6.9262604000000003</v>
@@ -3973,7 +3964,7 @@
         <v>335380</v>
       </c>
       <c r="K64" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L64" s="3">
         <f t="shared" si="1"/>
@@ -3989,19 +3980,19 @@
         <v>2127</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C65" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D65" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E65">
         <v>11300</v>
       </c>
       <c r="F65" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G65">
         <v>6.9737657000000004</v>
@@ -4016,7 +4007,7 @@
         <v>256815</v>
       </c>
       <c r="K65" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L65" s="3">
         <f t="shared" si="1"/>
@@ -4032,19 +4023,19 @@
         <v>2137</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C66" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D66" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E66">
         <v>11600</v>
       </c>
       <c r="F66" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G66">
         <v>6.9764094999999999</v>
@@ -4059,7 +4050,7 @@
         <v>251338</v>
       </c>
       <c r="K66" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L66" s="3">
         <f t="shared" si="1"/>
@@ -4075,19 +4066,19 @@
         <v>2144</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C67" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D67" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E67">
         <v>10390</v>
       </c>
       <c r="F67" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G67">
         <v>6.8248229</v>
@@ -4102,7 +4093,7 @@
         <v>218963</v>
       </c>
       <c r="K67" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L67" s="3">
         <f t="shared" si="1"/>
@@ -4121,16 +4112,16 @@
         <v>23</v>
       </c>
       <c r="C68" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D68" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E68">
         <v>10350</v>
       </c>
       <c r="F68" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G68">
         <v>6.8513853999999998</v>
@@ -4145,14 +4136,14 @@
         <v>247002</v>
       </c>
       <c r="K68" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L68" s="3">
         <f t="shared" si="1"/>
         <v>45901</v>
       </c>
       <c r="M68" s="3">
-        <f t="shared" ref="M68:M78" si="2">$M$2</f>
+        <f t="shared" ref="M68:M77" si="2">$M$2</f>
         <v>46292</v>
       </c>
     </row>
@@ -4161,19 +4152,19 @@
         <v>2110</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C69" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D69" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E69">
         <v>10300</v>
       </c>
       <c r="F69" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G69">
         <v>6.7962910000000001</v>
@@ -4188,7 +4179,7 @@
         <v>255036</v>
       </c>
       <c r="K69" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L69" s="3">
         <f t="shared" si="1"/>
@@ -4204,19 +4195,19 @@
         <v>2148</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C70" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D70" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E70">
         <v>10115</v>
       </c>
       <c r="F70" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G70">
         <v>6.9024998000000002</v>
@@ -4231,7 +4222,7 @@
         <v>88221</v>
       </c>
       <c r="K70" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L70" s="3">
         <f t="shared" si="1"/>
@@ -4247,19 +4238,19 @@
         <v>2146</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C71" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D71" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E71">
         <v>12500</v>
       </c>
       <c r="F71" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G71">
         <v>6.7103197000000003</v>
@@ -4274,7 +4265,7 @@
         <v>116961</v>
       </c>
       <c r="K71" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L71" s="3">
         <f t="shared" si="1"/>
@@ -4293,16 +4284,16 @@
         <v>12</v>
       </c>
       <c r="C72" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D72" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E72">
         <v>1200</v>
       </c>
       <c r="F72" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G72">
         <v>6.9385243000000001</v>
@@ -4317,7 +4308,7 @@
         <v>415715</v>
       </c>
       <c r="K72" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="L72" s="3">
         <f t="shared" si="1"/>
@@ -4333,19 +4324,19 @@
         <v>2149</v>
       </c>
       <c r="B73" t="s">
+        <v>284</v>
+      </c>
+      <c r="C73" t="s">
+        <v>285</v>
+      </c>
+      <c r="D73" t="s">
         <v>286</v>
-      </c>
-      <c r="C73" t="s">
-        <v>287</v>
-      </c>
-      <c r="D73" t="s">
-        <v>288</v>
       </c>
       <c r="E73">
         <v>10150</v>
       </c>
       <c r="F73" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G73">
         <v>6.8796799999999996</v>
@@ -4360,7 +4351,7 @@
         <v>109585</v>
       </c>
       <c r="K73" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L73" s="3">
         <f t="shared" si="1"/>
@@ -4376,19 +4367,19 @@
         <v>2104</v>
       </c>
       <c r="B74" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C74" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D74" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E74">
         <v>10300</v>
       </c>
       <c r="F74" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G74">
         <v>6.8006384999999998</v>
@@ -4403,7 +4394,7 @@
         <v>466684</v>
       </c>
       <c r="K74" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L74" s="3">
         <f t="shared" si="1"/>
@@ -4419,19 +4410,19 @@
         <v>2150</v>
       </c>
       <c r="B75" t="s">
+        <v>291</v>
+      </c>
+      <c r="C75" t="s">
+        <v>292</v>
+      </c>
+      <c r="D75" t="s">
         <v>293</v>
-      </c>
-      <c r="C75" t="s">
-        <v>294</v>
-      </c>
-      <c r="D75" t="s">
-        <v>295</v>
       </c>
       <c r="E75">
         <v>10230</v>
       </c>
       <c r="F75" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G75">
         <v>6.8393620000000004</v>
@@ -4446,7 +4437,7 @@
         <v>42366</v>
       </c>
       <c r="K75" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L75" s="3">
         <f t="shared" si="1"/>
@@ -4462,19 +4453,19 @@
         <v>2105</v>
       </c>
       <c r="B76" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C76" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D76" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E76">
         <v>12500</v>
       </c>
       <c r="F76" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G76">
         <v>6.7464633999999997</v>
@@ -4489,7 +4480,7 @@
         <v>178083</v>
       </c>
       <c r="K76" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L76" s="3">
         <f t="shared" si="1"/>
@@ -4505,13 +4496,13 @@
         <v>2151</v>
       </c>
       <c r="B77" t="s">
+        <v>297</v>
+      </c>
+      <c r="C77" t="s">
+        <v>298</v>
+      </c>
+      <c r="D77" t="s">
         <v>299</v>
-      </c>
-      <c r="C77" t="s">
-        <v>300</v>
-      </c>
-      <c r="D77" t="s">
-        <v>301</v>
       </c>
       <c r="G77">
         <v>6.8558665000000003</v>
@@ -4526,56 +4517,13 @@
         <v>8258</v>
       </c>
       <c r="K77" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L77" s="3">
         <f t="shared" si="1"/>
         <v>45901</v>
       </c>
       <c r="M77" s="3">
-        <f t="shared" si="2"/>
-        <v>46292</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A78">
-        <v>2079</v>
-      </c>
-      <c r="B78" t="s">
-        <v>26</v>
-      </c>
-      <c r="C78" t="s">
-        <v>79</v>
-      </c>
-      <c r="D78" t="s">
-        <v>79</v>
-      </c>
-      <c r="E78">
-        <v>0</v>
-      </c>
-      <c r="F78" t="s">
-        <v>302</v>
-      </c>
-      <c r="G78">
-        <v>6.9954109999999998</v>
-      </c>
-      <c r="H78">
-        <v>79.892482900000005</v>
-      </c>
-      <c r="I78">
-        <v>8799086</v>
-      </c>
-      <c r="J78">
-        <v>0</v>
-      </c>
-      <c r="K78" t="s">
-        <v>97</v>
-      </c>
-      <c r="L78" s="3">
-        <f t="shared" si="1"/>
-        <v>45901</v>
-      </c>
-      <c r="M78" s="3">
         <f t="shared" si="2"/>
         <v>46292</v>
       </c>
